--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -23170,6 +23170,154 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23203,7 +23351,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -23296,7 +23444,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -23348,7 +23496,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5719</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>79</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>25</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.4447022927160344</v>
       </c>
@@ -1554,9 +1548,6 @@
       <c r="O6" t="n">
         <v>35</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.6191415390284272</v>
       </c>
@@ -2199,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2346,9 +2337,6 @@
       <c r="O10" t="n">
         <v>38</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.3551054562747671</v>
       </c>
@@ -4074,9 +4062,6 @@
       <c r="O21" t="n">
         <v>88</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4467,9 +4452,6 @@
       <c r="O23" t="n">
         <v>21</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.3735499258814688</v>
       </c>
@@ -4863,9 +4845,6 @@
       <c r="O25" t="n">
         <v>35</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.6191415390284272</v>
       </c>
@@ -5508,7 +5487,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -5655,9 +5634,6 @@
       <c r="O29" t="n">
         <v>41</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.3831400975596171</v>
       </c>
@@ -7235,9 +7211,6 @@
       <c r="O39" t="n">
         <v>81</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="S39" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7628,9 +7601,6 @@
       <c r="O41" t="n">
         <v>34</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.6047951180938068</v>
       </c>
@@ -8024,9 +7994,6 @@
       <c r="O43" t="n">
         <v>44</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.7783493633500227</v>
       </c>
@@ -8669,7 +8636,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -8816,9 +8783,6 @@
       <c r="O47" t="n">
         <v>41</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.3831400975596171</v>
       </c>
@@ -10396,9 +10360,6 @@
       <c r="O57" t="n">
         <v>83</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10789,9 +10750,6 @@
       <c r="O59" t="n">
         <v>25</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.4447022927160344</v>
       </c>
@@ -11185,9 +11143,6 @@
       <c r="O61" t="n">
         <v>32</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.566072264254562</v>
       </c>
@@ -11581,9 +11536,6 @@
       <c r="O63" t="n">
         <v>67</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>1.267144512536125</v>
       </c>
@@ -11830,7 +11782,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -11977,9 +11929,6 @@
       <c r="O65" t="n">
         <v>42</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.3924849779879006</v>
       </c>
@@ -13557,9 +13506,6 @@
       <c r="O75" t="n">
         <v>55</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="S75" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13950,9 +13896,6 @@
       <c r="O77" t="n">
         <v>15</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.2668213756296206</v>
       </c>
@@ -14346,9 +14289,6 @@
       <c r="O79" t="n">
         <v>29</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.5130029894806968</v>
       </c>
@@ -14742,9 +14682,6 @@
       <c r="O81" t="n">
         <v>78</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>1.475183163848027</v>
       </c>
@@ -14991,7 +14928,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -15138,9 +15075,6 @@
       <c r="O83" t="n">
         <v>36</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.3364156954182004</v>
       </c>
@@ -16866,9 +16800,6 @@
       <c r="O94" t="n">
         <v>131</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.03753199953927895</v>
       </c>
@@ -17014,9 +16945,6 @@
       <c r="O95" t="n">
         <v>18</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.3201856507555447</v>
       </c>
@@ -17410,9 +17338,6 @@
       <c r="O97" t="n">
         <v>26</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.4599337147068316</v>
       </c>
@@ -17806,9 +17731,6 @@
       <c r="O99" t="n">
         <v>48</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.9078050239064779</v>
       </c>
@@ -18055,7 +17977,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -18202,9 +18124,6 @@
       <c r="O101" t="n">
         <v>26</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.242966891135367</v>
       </c>
@@ -18598,9 +18517,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -18746,9 +18662,6 @@
       <c r="O104" t="n">
         <v>163</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.04670012156414098</v>
       </c>
@@ -18894,9 +18807,6 @@
       <c r="O105" t="n">
         <v>2</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -19042,9 +18952,6 @@
       <c r="O106" t="n">
         <v>162</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.04641361775086404</v>
       </c>
@@ -19190,9 +19097,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -19338,9 +19242,6 @@
       <c r="O108" t="n">
         <v>137</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.03925102241894058</v>
       </c>
@@ -19486,9 +19387,6 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -19634,9 +19532,6 @@
       <c r="O110" t="n">
         <v>139</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.03982403004549445</v>
       </c>
@@ -19782,9 +19677,6 @@
       <c r="O111" t="n">
         <v>22</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.3913380175901103</v>
       </c>
@@ -20178,9 +20070,6 @@
       <c r="O113" t="n">
         <v>29</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.5130029894806968</v>
       </c>
@@ -20574,9 +20463,6 @@
       <c r="O115" t="n">
         <v>23</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.214932249850517</v>
       </c>
@@ -20970,9 +20856,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -21118,9 +21001,6 @@
       <c r="O118" t="n">
         <v>104</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.0297963965808016</v>
       </c>
@@ -21266,9 +21146,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -21414,9 +21291,6 @@
       <c r="O120" t="n">
         <v>139</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.03982403004549445</v>
       </c>
@@ -21562,9 +21436,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -21710,9 +21581,6 @@
       <c r="O122" t="n">
         <v>167</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.04784613681724874</v>
       </c>
@@ -21858,9 +21726,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22006,9 +21871,6 @@
       <c r="O124" t="n">
         <v>209</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.05987929697488016</v>
       </c>
@@ -22154,9 +22016,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22297,16 +22156,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R126" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -22459,10 +22315,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -22693,16 +22549,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O128" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R128" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22855,10 +22708,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O129" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -23094,9 +22947,6 @@
       <c r="O130" t="n">
         <v>183</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.05243019782967975</v>
       </c>
@@ -23242,9 +23092,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -23315,6 +23162,151 @@
       <c r="BC131" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>162</v>
+      </c>
+      <c r="O132" t="n">
+        <v>162</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.04641361775086404</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23351,7 +23343,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -23434,7 +23426,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -23444,7 +23436,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -23496,7 +23488,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5720</v>
+        <v>5893</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -22156,13 +22156,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R126" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -22315,10 +22315,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5893</v>
+        <v>5894</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O2" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O21" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O22" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O39" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O40" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -13501,10 +13501,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O75" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O76" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -16901,12 +16901,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16940,22 +16940,19 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="O95" t="n">
-        <v>18</v>
-      </c>
-      <c r="R95" t="n">
-        <v>0.3201856507555447</v>
+        <v>65</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -16975,12 +16972,12 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -16988,47 +16985,47 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17060,12 +17057,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -17099,24 +17096,24 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="O96" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
@@ -17131,7 +17128,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -17146,7 +17143,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -17181,17 +17178,17 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
+          <t>PHO IDTO current-year monthly preliminary giardiasis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -17209,12 +17206,12 @@
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -17222,47 +17219,47 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17294,12 +17291,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17333,13 +17330,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="O97" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R97" t="n">
-        <v>0.4599337147068316</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -17348,7 +17345,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -17368,12 +17365,12 @@
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -17381,47 +17378,47 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17453,12 +17450,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17492,24 +17489,24 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="O98" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
@@ -17539,7 +17536,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -17574,17 +17571,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -17602,12 +17599,12 @@
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -17615,47 +17612,47 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17687,12 +17684,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17726,13 +17723,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="O99" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="R99" t="n">
-        <v>0.9078050239064779</v>
+        <v>0.4599337147068316</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -17741,7 +17738,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -17766,7 +17763,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -17779,42 +17776,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17846,12 +17843,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -17885,24 +17882,24 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="O100" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
@@ -17917,7 +17914,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -17932,7 +17929,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -17967,17 +17964,17 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly giardiasis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -18000,7 +17997,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -18013,42 +18010,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18080,12 +18077,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -18119,13 +18116,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="O101" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="R101" t="n">
-        <v>0.242966891135367</v>
+        <v>0.9078050239064779</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -18134,7 +18131,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -18159,7 +18156,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -18172,42 +18169,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18239,12 +18236,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -18278,29 +18275,29 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="O102" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Giardiainfektion</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -18310,7 +18307,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -18325,7 +18322,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -18360,17 +18357,17 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly giardiasis notifications.</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18393,7 +18390,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -18406,42 +18403,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18473,12 +18470,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18503,7 +18500,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -18512,81 +18509,95 @@
         </is>
       </c>
       <c r="N103" t="n">
+        <v>26</v>
+      </c>
+      <c r="O103" t="n">
+        <v>26</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.242966891135367</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
         <v>1</v>
       </c>
-      <c r="O103" t="n">
-        <v>1</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP103" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
-      <c r="AT103" t="n">
-        <v>0</v>
-      </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18613,17 +18624,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18648,7 +18659,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -18657,81 +18668,170 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>163</v>
+        <v>26</v>
       </c>
       <c r="O104" t="n">
-        <v>163</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0.04670012156414098</v>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN104" t="b">
+        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18793,7 +18893,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -18802,13 +18902,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -18938,7 +19038,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -18947,13 +19047,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O106" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R106" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.04670012156414098</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19083,7 +19183,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19092,13 +19192,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19228,7 +19328,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19237,13 +19337,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="O108" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="R108" t="n">
-        <v>0.03925102241894058</v>
+        <v>0.04641361775086404</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19373,7 +19473,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -19382,13 +19482,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -19518,7 +19618,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -19527,13 +19627,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O110" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R110" t="n">
-        <v>0.03982403004549445</v>
+        <v>0.03925102241894058</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19633,12 +19733,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19663,104 +19763,90 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19787,17 +19873,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19822,179 +19908,90 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="O112" t="n">
-        <v>22</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
+        <v>139</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.03982403004549445</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20026,12 +20023,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20065,13 +20062,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="O113" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="R113" t="n">
-        <v>0.5130029894806968</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20080,7 +20077,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -20100,12 +20097,12 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -20113,47 +20110,47 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20185,12 +20182,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20224,24 +20221,24 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="O114" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -20271,7 +20268,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -20306,17 +20303,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -20334,12 +20331,12 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -20347,47 +20344,47 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20419,12 +20416,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20458,13 +20455,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O115" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R115" t="n">
-        <v>0.214932249850517</v>
+        <v>0.5130029894806968</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20473,7 +20470,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -20498,7 +20495,7 @@
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -20511,42 +20508,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20578,12 +20575,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20617,29 +20614,29 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O116" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>Giardiainfektion</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -20664,7 +20661,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -20699,17 +20696,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -20732,7 +20729,7 @@
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -20745,42 +20742,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20812,12 +20809,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20842,7 +20839,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -20851,81 +20848,95 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>0.214932249850517</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20952,17 +20963,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20987,7 +20998,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20996,81 +21007,170 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="O118" t="n">
-        <v>104</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0.0297963965808016</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21132,7 +21232,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21141,13 +21241,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -21277,7 +21377,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21286,13 +21386,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="O120" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="R120" t="n">
-        <v>0.03982403004549445</v>
+        <v>0.0297963965808016</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -21422,7 +21522,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21567,7 +21667,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21576,13 +21676,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="O122" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="R122" t="n">
-        <v>0.04784613681724874</v>
+        <v>0.03982403004549445</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21712,7 +21812,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21721,13 +21821,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21857,7 +21957,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -21866,13 +21966,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="O124" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="R124" t="n">
-        <v>0.05987929697488016</v>
+        <v>0.04784613681724874</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22002,7 +22102,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -22117,12 +22217,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22147,104 +22247,90 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>4</v>
+        <v>209</v>
       </c>
       <c r="O126" t="n">
-        <v>4</v>
+        <v>209</v>
       </c>
       <c r="R126" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.05987929697488016</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22271,17 +22357,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22306,179 +22392,90 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>4</v>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN127" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22510,12 +22507,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22549,13 +22546,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O128" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="R128" t="n">
-        <v>0.2476566156113709</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22564,7 +22561,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -22584,12 +22581,12 @@
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -22597,47 +22594,47 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22669,12 +22666,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22708,24 +22705,24 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O129" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
@@ -22755,7 +22752,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -22790,17 +22787,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -22818,12 +22815,12 @@
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -22831,47 +22828,47 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22903,12 +22900,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22942,81 +22939,95 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>183</v>
+        <v>14</v>
       </c>
       <c r="O130" t="n">
-        <v>183</v>
+        <v>14</v>
       </c>
       <c r="R130" t="n">
-        <v>0.05243019782967975</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23043,17 +23054,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23078,7 +23089,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -23087,81 +23098,170 @@
         </is>
       </c>
       <c r="N131" t="n">
+        <v>14</v>
+      </c>
+      <c r="O131" t="n">
+        <v>14</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
         <v>1</v>
       </c>
-      <c r="O131" t="n">
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
         <v>1</v>
       </c>
-      <c r="R131" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP131" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
-      <c r="AT131" t="n">
-        <v>0</v>
-      </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23323,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -23232,13 +23332,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="O132" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="R132" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.05243019782967975</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23305,6 +23405,296 @@
         </is>
       </c>
       <c r="BC132" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>162</v>
+      </c>
+      <c r="O134" t="n">
+        <v>162</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.04641361775086404</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -23426,7 +23816,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -23436,7 +23826,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -23456,7 +23846,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -23488,7 +23878,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5894</v>
+        <v>5969</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -22546,13 +22546,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R128" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22705,10 +22705,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -23697,6 +23697,151 @@
       <c r="BC134" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23733,7 +23878,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -23816,7 +23961,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -23826,7 +23971,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -23878,7 +24023,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5969</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -22546,13 +22546,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O128" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R128" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22705,10 +22705,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -22939,13 +22939,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O130" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="R130" t="n">
-        <v>0.2476566156113709</v>
+        <v>0.4599337147068316</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -23098,10 +23098,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O131" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -23842,6 +23842,151 @@
       <c r="BC135" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>171</v>
+      </c>
+      <c r="O136" t="n">
+        <v>171</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.0489921520703565</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23878,7 +24023,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -23961,7 +24106,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -23971,7 +24116,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -24023,7 +24168,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5971</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -22546,13 +22546,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R128" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22705,10 +22705,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6156</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -18116,13 +18116,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O101" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R101" t="n">
-        <v>0.9078050239064779</v>
+        <v>0.8888924192417595</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -18275,10 +18275,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O102" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -20809,12 +20809,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20848,13 +20848,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="O117" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="R117" t="n">
-        <v>0.214932249850517</v>
+        <v>1.078018465888942</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -20901,42 +20901,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20968,12 +20968,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -21007,29 +21007,29 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="O118" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>Giardiainfektion</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -21089,17 +21089,17 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly giardiasis notifications.</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -21122,7 +21122,7 @@
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
@@ -21135,42 +21135,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21202,12 +21202,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21241,81 +21241,95 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>0.214932249850517</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21342,17 +21356,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21377,7 +21391,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21386,81 +21400,170 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="O120" t="n">
-        <v>104</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0.0297963965808016</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21522,7 +21625,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21531,13 +21634,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21667,7 +21770,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21676,13 +21779,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="O122" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="R122" t="n">
-        <v>0.03982403004549445</v>
+        <v>0.0297963965808016</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21812,7 +21915,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21957,7 +22060,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -21966,13 +22069,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="O124" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="R124" t="n">
-        <v>0.04784613681724874</v>
+        <v>0.03982403004549445</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22102,7 +22205,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -22111,13 +22214,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -22247,7 +22350,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -22256,13 +22359,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="O126" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="R126" t="n">
-        <v>0.05987929697488016</v>
+        <v>0.04784613681724874</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -22392,7 +22495,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22507,12 +22610,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22537,104 +22640,90 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>8</v>
+        <v>209</v>
       </c>
       <c r="O128" t="n">
-        <v>8</v>
+        <v>209</v>
       </c>
       <c r="R128" t="n">
-        <v>0.142304733669131</v>
+        <v>0.05987929697488016</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22661,17 +22750,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22696,179 +22785,90 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>8</v>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22900,12 +22900,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22939,13 +22939,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="O130" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="R130" t="n">
-        <v>0.4599337147068316</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -22974,12 +22974,12 @@
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -22987,47 +22987,47 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23059,12 +23059,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23098,24 +23098,24 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="O131" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -23145,7 +23145,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -23180,17 +23180,17 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -23208,12 +23208,12 @@
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT131" t="n">
@@ -23221,47 +23221,47 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23293,12 +23293,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23332,81 +23332,95 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="O132" t="n">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="R132" t="n">
-        <v>0.05243019782967975</v>
+        <v>0.548382505996607</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23433,17 +23447,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23468,7 +23482,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -23477,81 +23491,170 @@
         </is>
       </c>
       <c r="N133" t="n">
+        <v>31</v>
+      </c>
+      <c r="O133" t="n">
+        <v>31</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
         <v>1</v>
       </c>
-      <c r="O133" t="n">
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
         <v>1</v>
       </c>
-      <c r="R133" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP133" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
-      <c r="AT133" t="n">
-        <v>0</v>
-      </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23716,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23622,13 +23725,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="O134" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="R134" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.05243019782967975</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23758,7 +23861,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23903,7 +24006,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23912,13 +24015,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="O136" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="R136" t="n">
-        <v>0.0489921520703565</v>
+        <v>0.04641361775086404</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23987,6 +24090,441 @@
       <c r="BC136" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>171</v>
+      </c>
+      <c r="O138" t="n">
+        <v>171</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.0489921520703565</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24023,7 +24561,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -24106,7 +24644,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -24116,7 +24654,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -24136,7 +24674,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -24168,7 +24706,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6157</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -24528,6 +24528,151 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>172</v>
+      </c>
+      <c r="O140" t="n">
+        <v>172</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.04927865588363343</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24561,7 +24706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -24644,7 +24789,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -24654,7 +24799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -24706,7 +24851,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6222</v>
+        <v>6394</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1188,17 +1188,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1422,17 +1427,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1573,7 +1583,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1581,17 +1591,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1807,7 +1822,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1815,17 +1830,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2362,7 +2382,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2370,17 +2390,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2596,7 +2621,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2604,17 +2629,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -4477,7 +4507,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4485,17 +4515,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4711,7 +4746,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -4719,17 +4754,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -4870,7 +4910,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -4878,17 +4918,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5104,7 +5149,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5112,17 +5157,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5659,7 +5709,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -5667,17 +5717,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5893,7 +5948,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -5901,17 +5956,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -7626,7 +7686,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -7634,17 +7694,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -7860,7 +7925,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -7868,17 +7933,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8019,7 +8089,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8027,17 +8097,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8253,7 +8328,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8261,17 +8336,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -8808,7 +8888,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8816,17 +8896,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9042,7 +9127,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9050,17 +9135,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -10775,7 +10865,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -10783,17 +10873,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -11009,7 +11104,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -11017,17 +11112,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -11168,7 +11268,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -11176,17 +11276,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -11402,7 +11507,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -11410,17 +11515,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -11954,7 +12064,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -11962,17 +12072,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -12188,7 +12303,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -12196,17 +12311,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13921,7 +14041,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -13929,17 +14049,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -14155,7 +14280,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -14163,17 +14288,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -14314,7 +14444,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -14322,17 +14452,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS79" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -14548,7 +14683,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -14556,17 +14691,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -15100,7 +15240,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -15108,17 +15248,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -15334,7 +15479,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -15342,17 +15487,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -17360,7 +17510,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -17368,17 +17518,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS97" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -17594,7 +17749,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -17602,17 +17757,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS98" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -17753,7 +17913,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -17761,17 +17921,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -17987,7 +18152,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
@@ -17995,17 +18160,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS100" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -18539,7 +18709,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -18547,17 +18717,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -18773,7 +18948,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -18781,17 +18956,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -20092,7 +20272,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
@@ -20100,17 +20280,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS113" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -20326,7 +20511,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
@@ -20334,17 +20519,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS114" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -20485,7 +20675,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -20493,17 +20683,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS115" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -20719,7 +20914,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -20727,17 +20922,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -21271,7 +21471,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
@@ -21279,17 +21479,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS119" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -21505,7 +21710,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -21513,17 +21718,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GIARDIA</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -22969,7 +23179,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
@@ -22977,17 +23187,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS130" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -23203,7 +23418,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
@@ -23211,17 +23426,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS131" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -23362,7 +23582,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
@@ -23370,17 +23590,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS132" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -23596,7 +23821,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -23604,17 +23829,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -23149,13 +23149,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O130" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R130" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -23313,10 +23313,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O131" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -23552,13 +23552,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="O132" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="R132" t="n">
-        <v>0.548382505996607</v>
+        <v>0.7606596050920676</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23716,10 +23716,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="O133" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -24900,6 +24900,1102 @@
       <c r="BC140" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>200</v>
+      </c>
+      <c r="O142" t="n">
+        <v>200</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.05730076265538771</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="n">
+        <v>1</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="n">
+        <v>1</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24936,7 +26032,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -25019,7 +26115,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -25029,7 +26125,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -25049,7 +26145,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -25081,7 +26177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6394</v>
+        <v>6611</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -25260,13 +25260,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R143" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -25424,10 +25424,10 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6611</v>
+        <v>6612</v>
       </c>
     </row>
     <row r="16">
